--- a/datasets/MPESA_Marylyne.xlsx
+++ b/datasets/MPESA_Marylyne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/briankimanzi/Documents/programming Languages/PythonProgramming/JupyterNoteBook/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0C455A-34DF-5946-953D-40C037D77CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3377FA5E-138F-4F49-A6F3-1517CEB58755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
